--- a/projects/offline_asr_llm_aiot_iis_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/projects/offline_asr_llm_aiot_iis_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="&lt;0&gt;cmd" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="introduction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="&lt;1&gt;wake" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="introduction" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -572,7 +573,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -594,7 +595,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>REFUSE-RECOGNIZE</t>
+          <t>HI-VITANA</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -606,11 +607,11 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -629,7 +630,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -637,26 +638,26 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="2" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>CANCEL-VOICE-CONTROL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10001</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x0003</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -687,18 +688,18 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>&lt;welcome&gt;</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -737,112 +738,161 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>&lt;beep&gt;</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>10003</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>0x00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>user_defined</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" t="inlineStr">
         <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" s="2" t="n">
         <v>43605</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>user_defined</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M8" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2 H2 I2 J2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="G2 G3 G4 H2 H3 H4 I2 I3 I4 J2 J3 J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="L2 L3 L4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>
@@ -851,6 +901,482 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>modelName</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>modelFileID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>commandWord</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>commandID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>semanticID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>confidThresh</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>wakeWordTag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>reserved1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>reserved2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>reserved3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>validRecogCnt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>promptPlayOpt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>prompt0ID</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>prompt1ID</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AcousticModel</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VITANA</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LanguageModel</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HI-VITANA</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0x0002</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CANCEL-VOICE-CONTROL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0x0003</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>&lt;beep&gt;</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>&lt;baud_sync_req&gt;</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>43605</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0xAA55</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="G2 G3 G4 H2 H3 H4 I2 I3 I4 J2 J3 J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2 L3 L4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+      <formula1>"user_defined,random"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/projects/offline_asr_llm_aiot_iis_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/projects/offline_asr_llm_aiot_iis_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -761,7 +761,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>18</v>
@@ -802,7 +802,7 @@
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>18</v>
@@ -1095,7 +1095,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>18</v>
@@ -1136,7 +1136,7 @@
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>18</v>

--- a/projects/offline_asr_llm_aiot_iis_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/projects/offline_asr_llm_aiot_iis_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\CI130X_SDK_LLM_AIOT_V3.0.13\projects\offline_asr_llm_aiot_iis_sample\firmware\user_file\cmd_info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72A67D6-F6E9-4E33-8254-644A38446706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8513A458-238C-418C-8753-F41DA493C4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6888" yWindow="3768" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9132" yWindow="4620" windowWidth="21180" windowHeight="12144" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="&lt;0&gt;cmd" sheetId="1" r:id="rId1"/>
